--- a/lynkk-reddit-leads/results/2026-10-11/reply_drafts_2026-10-11.xlsx
+++ b/lynkk-reddit-leads/results/2026-10-11/reply_drafts_2026-10-11.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reply drafts" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="reply drafts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +501,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -509,17 +509,17 @@
           <t>https://www.reddit.com/r/AIAssisted/comments/1wq1m2t/which_ai_meeting_note_taker_are_you_using/</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>r/AIAssisted</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>u/Rist0o0</t>
         </is>
@@ -541,11 +541,11 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>If your in-person meetings happen where a laptop is open, you may not need a separate recorder; a laptop mic is fine for a small room, and having everything in one place matters more than people expect. A recorder makes sense for site visits or coffee meetings.
-I work on Lynkk, so I'm biased, but it covers both from one account: the Mac app or Chrome extension records online calls without a bot joining, and in person you can record from the laptop mic in the browser. Each meeting gets a brief with decisions and action items, and the timestamps play the recording from that moment. It's Mac and web only, no phone app.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+          <t>Depends a lot on where your in-person meetings happen. If there's usually a laptop on the table anyway, I'd try recording from that before buying a Plaud or Pocket. A laptop mic is fine for a small room, and you end up with everything in one app instead of two, which you'll appreciate when you're looking for something from three weeks ago. A recorder makes more sense if you're often in cafes or on site.
+Full disclosure, I work on Lynkk, which does that combo (calls without a bot, in-person from the browser), so I'm biased. But the one-place thing matters whichever tool you pick.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -557,7 +557,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -565,17 +565,17 @@
           <t>https://www.reddit.com/r/PLAUDAI/comments/1x1tha4/lawyers_using_plaud_or_other_ai_notetakers_for/</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>r/PLAUDAI</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>u/Party_History2839</t>
         </is>
@@ -597,11 +597,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>For in-person consults, a cheap USB boundary mic on the table helps accuracy more than switching apps. For the weeks-later problem, judge tools on whether the summary keeps decisions and open questions with timestamps back to the recording, so you can check exact wording before drafting.
-I work on Lynkk, so take this with that in mind. It records in-person meetings from the laptop mic in the browser and video calls through the Mac app with no bot joining. Each note gets a brief with decisions, open questions and action items, and every timestamp plays the recording from that moment. We never train on your conversations, but put your confidentiality questions to any vendor in writing, us included.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+          <t>The weeks-later gap is the real test, and most demos never show it. Record a consult, don't touch it for two weeks, then try to draft from the notes alone and see what's missing. Day-one summaries all look fine.
+Also +1 on a cheap boundary mic for in-person, it matters more than the app.
+I'm on the Lynkk team, so grain of salt, but if you want a software-only option to compare against Plaud Desktop, it records in the browser for in-person and through a Mac app for calls, and every point in the notes links back to the spot in the recording. Worth running the same consult through both.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -613,7 +614,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -621,17 +622,17 @@
           <t>https://www.reddit.com/r/AiNoteTaker/comments/1wzy65s/any_ai_tool_that_can_handle_both_online_and/</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>r/AiNoteTaker</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>u/jordanconnelly</t>
         </is>
@@ -653,11 +654,11 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Choose by where everything ends up, not how it records; one searchable library is what stops the digging.
-I work on Lynkk, so I'm biased. It handles two of your three: the Mac app notices Zoom, Meet, Teams, FaceTime and WhatsApp calls and records without a bot, and in-person meetings can be recorded from the laptop mic in the browser. Everything lands in one place, and you can ask questions across your notes by person, company or project. Honest gap: there's no phone app, so native iPhone calls aren't covered. Taking important calls through FaceTime or WhatsApp on the Mac gets them in too.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+          <t>Phone calls are the annoying one. Almost nothing can record a regular iPhone call, so people either take important calls on the laptop (FaceTime or WhatsApp desktop) or live with a separate app for those.
+Zoom plus in-person in one place is the easy part. Disclosure, I work on Lynkk, which handles those two and keeps them searchable together, but there's no phone app, so it wouldn't fix the iPhone bit. Whatever you go with, I'd rank 'one place to search' above anything else on the feature list.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -669,7 +670,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -677,17 +678,17 @@
           <t>https://www.reddit.com/r/AiNoteTaker/comments/1wm4zsu/can_any_ai_notetaker_show_how_a_decision_changed/</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>r/AiNoteTaker</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>u/FinishTough23</t>
         </is>
@@ -709,11 +710,11 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>I haven't seen anything that builds a clean decision changelog automatically, so it's a combination: summaries that keep decisions apart from concerns, questions asked across all of a project's meetings, and saying changes out loud on the call ('we're moving launch to November because of lead times').
-I work on Lynkk, so I'm biased. Its chat answers only from your own notes, can find notes by project, and lists decisions with citation chips that open the note at the exact moment, so you can click through each step and confirm a suggestion actually became an agreement. It's not a dedicated timeline view, but it covers the 'what's current and why' question.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+          <t>This is the thing summaries are worst at, because each one only knows its own meeting. What tends to work better is asking across the whole project ('what's the current launch date and when did it change?') and only trusting answers that point to the specific meeting and moment, so you can click through and see whether it was a real decision or just someone floating it.
+Disclosure, I work on Lynkk, and that's roughly how its chat works: answers from your own notes, with citations you can click. Not a proper decision timeline though. Would love to see someone build that.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -725,7 +726,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -733,17 +734,17 @@
           <t>https://www.reddit.com/r/softwaresworthpaying/comments/1wzp2i0/do_we_need_another_ai_meeting_note_taker_for/</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>r/softwaresworthpaying</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>u/BakerInfamous6110</t>
         </is>
@@ -765,11 +766,11 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Copilot covers meetings your tenant hosts, so customer links are the gap. For finance, count last month's important customer calls outside Teams; that number is the case. Keep Copilot for internal meetings and only add seats for people on external calls.
-I work on Lynkk, so I'm biased. The Mac app notices calls in Zoom, Google Meet, Teams, Slack huddles and Webex and records from the laptop with no bot, so it doesn't matter whose link it is. There's also a bot that can join Zoom, Meet and Teams links if you prefer. Caveat: the Mac app needs Apple silicon.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+          <t>Copilot's fine for internal stuff, but it really only covers meetings your tenant hosts, so customer calls on their Zoom links fall through. For the budget conversation I'd count how many important customer calls last month were outside Teams. That number usually settles it.
+If you do add something, look for one that records from the laptop instead of joining as a bot, then it doesn't matter whose link it is. (I work on Lynkk, which works that way on Mac, so yes, biased. Apple silicon only though.)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -781,7 +782,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -789,17 +790,17 @@
           <t>https://www.reddit.com/r/sales/comments/1wk7yt9/tablet_apps_and_ai_tools/</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>r/sales</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>u/throwaway09251975</t>
         </is>
@@ -821,11 +822,11 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Since customers are fine with recording, record instead of converting handwriting; you get a summary with next steps you didn't have to write, which maps straight onto a follow-up email.
-I work on Lynkk, so I'm biased. You can record an in-person meeting from a laptop mic in the browser and get a brief with decisions, action items with owners and due dates, and open questions. Honest limits: there's no tablet or phone app, and it doesn't sync to Salesforce, so the CRM step stays manual. If you're on a laptop in meetings anyway, it covers the notes and next steps part.</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+          <t>If customers are fine with recording, I'd skip the tablet and handwriting route. You'd still be summarizing your own notes afterwards. Record the meeting, let the tool pull the next steps, and the follow-up email is mostly done.
+Salesforce is where most of these tools get vague, so ask straight out whether it updates fields or just hands you text. Disclosure: I work on Lynkk, which covers the record and next steps part from a laptop, but it doesn't sync to Salesforce, so that bit would stay manual.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -837,7 +838,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -845,17 +846,17 @@
           <t>https://www.reddit.com/r/PlaudNoteUsers/comments/1x12i9y/what_ai_note_taking_apps_are_you_using_for/</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>r/PlaudNoteUsers</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>u/QuietlyKevin07</t>
         </is>
@@ -877,11 +878,11 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>For small details, what matters is whether the summary links back to the exact moment in the recording, and whether you can search across all meetings. Test with a real 60 to 90 minute call; that's where summaries get vague.
-I work on Lynkk, so I'm biased. Every takeaway in its brief has a timestamp that plays the recording from that moment, and you can ask questions across your notes and get answers with citations back to the moment. Recordings go up to 2 hours each. It's Mac, Chrome and web rather than a hardware recorder, so it suits calls and laptop-in-the-room meetings.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+          <t>The biggest difference on long meetings is whether you can jump from a line in the summary straight to that moment in the audio. Saves so much scrubbing. And test with a real 90 minute meeting, not a 10 minute demo; that's where summaries start getting mushy.
+(Disclosure: I work on Lynkk, which does the timestamp-to-audio thing, but it's Mac, Chrome and web, not a pocket recorder, so it's a different setup from Plaud.)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -893,7 +894,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -901,17 +902,17 @@
           <t>https://www.reddit.com/r/AgentsOfAI/comments/1wtfbyj/one_ai_meeting_note_taker_for_microsoft_teams_and/</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>r/AgentsOfAI</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>u/Then_Date1452</t>
         </is>
@@ -933,11 +934,11 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Pilot it on the external calls first. Watch for customers' Zoom settings holding bots in the waiting room, recordings landing in different places depending on host, and retention differing between personal and company accounts.
-I work on Lynkk, so I'm biased. It does both platforms from one archive: a bot that joins Teams, Zoom and Meet links (or auto-joins from the calendar), plus a Mac app and Chrome extension that record without a bot when a bot gets blocked. A workspace gives everyone Pro and keeps the record with the company. Limit: workspaces are up to 10 seats, so it fits a small team, not a big rollout.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+          <t>The thing that breaks in practice is external Zoom calls where the host's settings hold bots in the waiting room. So whatever you pick, make sure it can also record from the user's own machine as a fallback. Then run a two-week pilot with whoever lives on Zoom and just count how many external calls actually got captured.
+I'm on the Lynkk team, bias noted. It has a bot for Teams, Zoom and Meet plus a no-bot Mac app and Chrome extension for the blocked cases, all in one archive. Workspaces cap at 10 seats though, so only relevant if this client's team is small.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -949,7 +950,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -957,17 +958,17 @@
           <t>https://www.reddit.com/r/AIAssisted/comments/1wj0zra/what_ai_meeting_note_taker_are_you_actually_using/</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>r/AIAssisted</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>u/jimmybobjoeflow</t>
         </is>
@@ -977,7 +978,7 @@
           <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Good lead. Asks which note taker people use.</t>
         </is>
@@ -989,11 +990,11 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Some review is still worth it, but it can be a two-minute skim if decisions, action items and open questions are separate lists with timestamps back to the recording. Saying owners and deadlines out loud at the end of the call helps a lot too.
-I work on Lynkk, so I'm biased. Its meeting brief lists decisions with context, action items with owner, due date and priority, and open questions, and every timestamp plays the recording from that moment, so checking an item takes seconds. It records Zoom, Meet and Teams without a bot from the Mac app or Chrome extension.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+          <t>You'll probably always do some review, but it can be a two-minute skim instead of a reread. What cuts it down most is when every action item has a timestamp you can click to hear the original moment, so you only check the ones that look off. Saying owners and dates out loud at the end of the call helps a ton too.
+Disclosure, I work on Lynkk, which is built around that click-to-check idea. Honestly though, the verbal recap at the end helps with any tool.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1005,7 +1006,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1013,17 +1014,17 @@
           <t>https://www.reddit.com/r/AI_Agents/comments/1wq1vrs/any_fathom_ai_alternatives_that_work_better_with/</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>r/AI_Agents</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>u/Sash19</t>
         </is>
@@ -1045,11 +1046,11 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Two setups work: pipe transcripts into your agent (flexible, but the agent does the retrieval), or ask questions inside the notes tool if it searches across meetings and cites sources. For follow-ups and old decisions, the second is often enough.
-I work on Lynkk, so I'm biased. Its chat answers only from your own notes, finds them by person, company or project, lists open tasks and decisions with citations to the moment, and can take actions behind a confirm step, like creating a Jira issue or a calendar event. You can also ask it from Slack. It's a different shape from MCP, so it depends on whether you need your own agent in the loop.</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+          <t>Depends whether you need the meeting data inside your own agent or just need answers. If it's mostly 'what did we decide with X' and 'what's still open', asking inside the notes tool is simpler than wiring transcripts into an agent. If the agent needs to act on it alongside other context, then yeah, your MCP route makes sense.
+I work on Lynkk so I'm biased, but it's the first kind: you ask across your notes, get answers that link back to the moment, and can create a Jira issue from there. Not sure it fits if you need it inside your own agent.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1061,7 +1062,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1069,17 +1070,17 @@
           <t>https://www.reddit.com/r/AIWorkStack/comments/1x14cj5/are_ai_notetaking_tools_actually_better_than/</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>r/AIWorkStack</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>u/lebron7</t>
         </is>
@@ -1089,7 +1090,7 @@
           <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Disclosed vendor replies already appear in this thread.</t>
         </is>
@@ -1101,11 +1102,11 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Checking is the right instinct; the trick is making it fast. Timestamps on each takeaway that play the original moment turn verification into a ten-second job, and saying decisions and owners out loud at the end of the call makes summaries much more reliable.
-I work on Lynkk, so I'm biased. That's how its meeting brief works: every takeaway and action item has a timestamp that plays the recording from that moment, and you can search or ask questions across all your notes afterward. It records without a bot from the Mac app or Chrome extension, and in person from the browser.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+          <t>Checking is the right call. What makes it workable is being able to click a line in the summary and hear the original moment, so checking a detail takes seconds instead of rereading the transcript. Small details are exactly where summaries slip, so I'd trust the summary for the gist and the recording for names and numbers.
+(I work on Lynkk, so bias disclosed. It does the click-to-hear thing, plus search across all your meetings afterwards.)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1117,7 +1118,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1125,17 +1126,17 @@
           <t>https://www.reddit.com/r/MyAIAssistant/comments/1wjsca7/my_ai_summarized_a_meeting_and_invented_an_action/</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>r/MyAIAssistant</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>u/Morphius007</t>
         </is>
@@ -1157,11 +1158,11 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>The reliable fix is evidence: every action item should link to the moment it came from, and anything without a source stays a draft. Have owners confirm their own items, and end calls with a 60-second recap of owners and dates said out loud.
-I work on Lynkk, so I'm biased. Its brief keeps decisions, action items and open questions separate, and every item has a timestamp that plays the recording from that moment, so an invented 'Ship Phase 2 by Friday' is quick to catch because there's nothing to click back to. Sending items to Jira is a manual step, so nothing hits the board without a person.</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+          <t>That 'inferred urgency' thing is exactly why action items need a source. Simplest rule: every action item links to the moment it was said, and anything without a source stays a draft. That catches invented deadlines in seconds. Also have owners confirm their own items instead of the PM approving everything.
+Disclosure, I work on Lynkk. Its action items each carry a timestamp back to the recording, and nothing goes to Jira unless someone sends it by hand.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1173,7 +1174,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1181,17 +1182,17 @@
           <t>https://www.reddit.com/r/PLAUDAI/comments/1x1tha4/lawyers_using_plaud_or_other_ai_notetakers_for/pezdury/</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>r/PLAUDAI</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>u/Party_History2839</t>
         </is>
@@ -1213,11 +1214,10 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Reasonable worry. Whatever you pick, export regularly so you're never locked in, and pilot two tools on real consultations before committing firm-wide.
-I work on Lynkk, so I'm biased, but if you want a second tool to compare: it records consultations from the laptop mic in the browser and video calls through the Mac app without a bot, and gives a brief with decisions and open questions that link back to the recording. It's software only, so no hardware to commit to.</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+          <t>Totally fair worry. Whatever you pick, export your recordings regularly so you're never stuck, and do a short side-by-side with a second tool before recommending anything firm-wide. (I work on Lynkk, so I'm one of the options. It's software only, so there's no hardware to bet on.)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1229,7 +1229,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1237,17 +1237,17 @@
           <t>https://www.reddit.com/r/AIToolTalks/comments/1ws9lds/which_ai_meeting_note_taker_are_you_using/</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>r/AIToolTalks</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>u/Rist0o0</t>
         </is>
@@ -1269,11 +1269,10 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Depends on your mix, but keeping online and in-person meetings in one searchable place matters most.
-I work on Lynkk, so I'm biased. It records online calls without a bot from the Mac app or Chrome extension, records in-person meetings from the laptop mic in the browser, and gives each meeting a brief with decisions and action items linked back to the recording.</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+          <t>Mostly depends on whether you have in-person meetings too. If you do, keep everything in one tool, otherwise you end up searching two places later. I'm on the Lynkk team, which does calls without a bot plus in-person from the browser, but I'd give the same advice for any tool.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1285,7 +1284,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1293,17 +1292,17 @@
           <t>https://www.reddit.com/r/MyAIAssistant/comments/1wli9fz/my_meetingnotes_ai_invented_action_owners_who/</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>r/MyAIAssistant</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>u/Morphius007</t>
         </is>
@@ -1325,11 +1324,10 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>The stronger check than attendee lists is evidence: an owner should only be set when someone said it, with a link to that moment; otherwise it's 'owner needed'. A verbal recap of owners at the end of the call removes most of the guessing.
-I work on Lynkk, so I'm biased. Its action items carry owner, due date and priority, each with a timestamp that plays the recording from that moment, so you can check whether an owner was actually named before anything is sent on.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+          <t>Attendee-only is a good guardrail, but I'd go one step further: only set an owner when someone actually said it, with a link to that moment. Otherwise mark it 'owner needed'. A 30-second recap at the end ('Priya has the roadmap, Friday') removes most of the guessing. (Disclosure: I work on Lynkk, where every action item links back to the recording, which makes checking this pretty quick.)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1341,7 +1339,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1349,17 +1347,17 @@
           <t>https://www.reddit.com/r/PLAUDAI/comments/1x1tha4/lawyers_using_plaud_or_other_ai_notetakers_for/pezix4j/</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>r/PLAUDAI</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>u/Party_History2839</t>
         </is>
@@ -1381,11 +1379,10 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Fair reason to look around: if you need recording, transcription and a reliable summary, focus beats agent features. Test any alternative against your top three needs on a real consultation.
-I work on Lynkk, so I'm biased, but that's the core of what it does: record (browser for in-person, Mac app for calls, no bot), transcribe, and give a brief with decisions, open questions and action items that link back to the recording.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+          <t>Makes sense. If what you need is record, transcribe and summarize reliably, the agent features are just noise. I'd write down the three things you actually rely on and test alternatives against only those. (Biased, I work on Lynkk, which sticks to that core: recording, transcript, and a brief that links back to the audio.)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1397,7 +1394,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1405,17 +1402,17 @@
           <t>https://www.reddit.com/r/PLAUDAI/comments/1x1tha4/lawyers_using_plaud_or_other_ai_notetakers_for/pf1cu0o/</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>r/PLAUDAI</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>u/Overall_Fold7937</t>
         </is>
@@ -1437,11 +1434,10 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Mixed-language meetings are hard for most engines. Setting the languages up front and adding custom words for names helps, and a short hand-checked sample tells you if it's the audio or the model.
-I work on Lynkk, so I'm biased. It transcribes 17 languages with auto-detect (four of them in beta) and has a custom words dictionary, so it might be worth a side-by-side test on one of your mixed meetings.</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+          <t>Mixed language is rough for most engines. Setting the languages explicitly, if your tool lets you, and adding names and terms to a custom vocab usually helps more than anything. If you want a comparison point, I work on Lynkk, which does 17 languages with auto-detect plus a custom words list. Might be worth one side-by-side on a mixed meeting.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1453,7 +1449,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1461,17 +1457,17 @@
           <t>https://www.reddit.com/r/negotiation/comments/1x1qct6/is_there_an_ai_tool_that_can_tell_me_exactly/</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>r/negotiation</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>u/belligerent_vogue</t>
         </is>
@@ -1493,11 +1489,10 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Start with five lost and five won deals, and review only the stretch from first price mention onward; patterns show up fast across ten calls.
-I work on Lynkk, so I'm biased, and it isn't a coaching tool. But its Sales Call summary and timestamped takeaways let you jump to the price discussion instead of replaying an hour, and you can ask questions across calls with answers that cite the moment. It may help with the review time, not the scoring.</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+          <t>I'd start smaller than a coaching platform. Take five lost deals and five won ones and only listen from the first price mention onward. Patterns show up faster than you'd think. (I work on Lynkk. It's not a coaching tool, but its timestamps let you jump straight to the price discussion instead of replaying the whole hour, which might at least cut the review time.)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>
@@ -1509,7 +1504,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1517,17 +1512,17 @@
           <t>https://www.reddit.com/r/AIDiscussion/comments/1wymbzg/is_an_ai_meeting_assistant_saving_you_work_after/</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>post</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>r/AIDiscussion</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>u/Doug19</t>
         </is>
@@ -1549,11 +1544,10 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>The useful part is structure, not the summary: decisions, action items with owners, and open questions as separate lists, each linked to the moment it came from. 'We could try this' belongs in open questions.
-I work on Lynkk, so I'm biased. Its brief is built that way, with timestamps that play the recording, and without a bot from the Mac app or Chrome extension, which sounds like what you liked about Bluedot.</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+          <t>The summary itself rarely saves time. What helps is when 'we could try this' gets filed as an open question instead of a decision, and you can click back to hear how it was actually said. (Disclosure: I work on Lynkk, which records without a bot too. Curious what other people find actually gets opened after the meeting.)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>If you want to try it, there's a free plan at lynkk.ai.</t>
         </is>

--- a/lynkk-reddit-leads/results/2026-10-11/reply_drafts_2026-10-11.xlsx
+++ b/lynkk-reddit-leads/results/2026-10-11/reply_drafts_2026-10-11.xlsx
@@ -541,8 +541,8 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Depends a lot on where your in-person meetings happen. If there's usually a laptop on the table anyway, I'd try recording from that before buying a Plaud or Pocket. A laptop mic is fine for a small room, and you end up with everything in one app instead of two, which you'll appreciate when you're looking for something from three weeks ago. A recorder makes more sense if you're often in cafes or on site.
-Full disclosure, I work on Lynkk, which does that combo (calls without a bot, in-person from the browser), so I'm biased. But the one-place thing matters whichever tool you pick.</t>
+          <t>Depends on where your in-person meetings happen. If there's usually a laptop on the table, try recording from that before buying a Plaud or Pocket; a laptop mic is fine for a small room, and you get everything in one app instead of two. A recorder makes more sense for cafes or site visits.
+If you want one tool for both, Lynkk is worth a look: it records Zoom, Meet and Teams calls without a bot joining, and in-person meetings straight from the browser, so it all ends up searchable in one place.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -597,9 +597,8 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>The weeks-later gap is the real test, and most demos never show it. Record a consult, don't touch it for two weeks, then try to draft from the notes alone and see what's missing. Day-one summaries all look fine.
-Also +1 on a cheap boundary mic for in-person, it matters more than the app.
-I'm on the Lynkk team, so grain of salt, but if you want a software-only option to compare against Plaud Desktop, it records in the browser for in-person and through a Mac app for calls, and every point in the notes links back to the spot in the recording. Worth running the same consult through both.</t>
+          <t>The weeks-later gap is the real test, and demos never show it. Record a consult, leave it for two weeks, then try to draft from the notes alone and see what's missing. A cheap boundary mic on the table also matters more than the app for in-person.
+For a software-only comparison against Plaud Desktop, Lynkk is one to try: it records in-person consults in the browser and video calls through a Mac app, and every point in the notes links back to the exact spot in the recording, which helps when you're drafting weeks later.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -654,8 +653,8 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Phone calls are the annoying one. Almost nothing can record a regular iPhone call, so people either take important calls on the laptop (FaceTime or WhatsApp desktop) or live with a separate app for those.
-Zoom plus in-person in one place is the easy part. Disclosure, I work on Lynkk, which handles those two and keeps them searchable together, but there's no phone app, so it wouldn't fix the iPhone bit. Whatever you go with, I'd rank 'one place to search' above anything else on the feature list.</t>
+          <t>Phone calls are the hard part. Almost nothing can record a regular iPhone call, so the usual workaround is taking important calls on the laptop through FaceTime or WhatsApp desktop.
+For Zoom plus in-person in one place, Lynkk covers both: the Mac app picks up Zoom, Meet, Teams, FaceTime and WhatsApp calls without a bot, and in-person meetings can be recorded from the browser, all searchable together. No phone app though, so native iPhone calls stay the gap.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -710,8 +709,8 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>This is the thing summaries are worst at, because each one only knows its own meeting. What tends to work better is asking across the whole project ('what's the current launch date and when did it change?') and only trusting answers that point to the specific meeting and moment, so you can click through and see whether it was a real decision or just someone floating it.
-Disclosure, I work on Lynkk, and that's roughly how its chat works: answers from your own notes, with citations you can click. Not a proper decision timeline though. Would love to see someone build that.</t>
+          <t>Summaries are bad at this because each one only knows its own meeting. What works better is asking across the whole project ('what's the current launch date and when did it change?') and only trusting answers that point to the specific meeting and moment, so you can check whether it was a real decision or just someone floating an idea.
+Lynkk's chat works roughly that way: it answers only from your own notes, finds them by project, and every answer has citations that open the note at the exact moment. Not a dedicated decision timeline, but it handles the 'what's current and why' question.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -766,8 +765,8 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Copilot's fine for internal stuff, but it really only covers meetings your tenant hosts, so customer calls on their Zoom links fall through. For the budget conversation I'd count how many important customer calls last month were outside Teams. That number usually settles it.
-If you do add something, look for one that records from the laptop instead of joining as a bot, then it doesn't matter whose link it is. (I work on Lynkk, which works that way on Mac, so yes, biased. Apple silicon only though.)</t>
+          <t>Copilot only really covers meetings your tenant hosts, so customer calls on their Zoom links fall through. For the budget conversation, count how many important customer calls last month were outside Teams; that number usually settles it.
+If you add something, pick a tool that records from the laptop instead of joining as a bot, so it doesn't matter whose link it is. Lynkk's Mac app works like that across Zoom, Meet, Teams and Webex (Apple silicon Macs only).</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -822,8 +821,8 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>If customers are fine with recording, I'd skip the tablet and handwriting route. You'd still be summarizing your own notes afterwards. Record the meeting, let the tool pull the next steps, and the follow-up email is mostly done.
-Salesforce is where most of these tools get vague, so ask straight out whether it updates fields or just hands you text. Disclosure: I work on Lynkk, which covers the record and next steps part from a laptop, but it doesn't sync to Salesforce, so that bit would stay manual.</t>
+          <t>If customers are fine with recording, skip the tablet and handwriting route; you'd still be summarizing your own notes afterwards. Record the meeting, let the tool pull out next steps, and the follow-up email is mostly written.
+For in-person meetings from a laptop, Lynkk records in the browser and gives you decisions and action items with owners and due dates. It doesn't sync to Salesforce, so check that part with any tool you try, since most only hand you text.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -878,8 +877,8 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>The biggest difference on long meetings is whether you can jump from a line in the summary straight to that moment in the audio. Saves so much scrubbing. And test with a real 90 minute meeting, not a 10 minute demo; that's where summaries start getting mushy.
-(Disclosure: I work on Lynkk, which does the timestamp-to-audio thing, but it's Mac, Chrome and web, not a pocket recorder, so it's a different setup from Plaud.)</t>
+          <t>The biggest difference on long meetings is whether you can jump from a line in the summary straight to that moment in the audio; it saves a lot of scrubbing. Test with a real 90-minute meeting, not a short demo, because that's where summaries go vague.
+Lynkk does the timestamp-to-audio part well: every takeaway plays the recording from that moment. It's Mac, Chrome and web rather than a pocket recorder, so it's a different setup from Plaud.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,8 +933,8 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>The thing that breaks in practice is external Zoom calls where the host's settings hold bots in the waiting room. So whatever you pick, make sure it can also record from the user's own machine as a fallback. Then run a two-week pilot with whoever lives on Zoom and just count how many external calls actually got captured.
-I'm on the Lynkk team, bias noted. It has a bot for Teams, Zoom and Meet plus a no-bot Mac app and Chrome extension for the blocked cases, all in one archive. Workspaces cap at 10 seats though, so only relevant if this client's team is small.</t>
+          <t>What usually breaks is external Zoom calls where the host's settings hold bots in the waiting room, so make sure whatever you pick can also record from the user's own machine. Then pilot it for two weeks with the heaviest Zoom users and count how many external calls actually got captured.
+Lynkk handles both cases in one archive: a bot for Teams, Zoom and Meet, plus a no-bot Mac app and Chrome extension for when bots get blocked. Workspaces cap at 10 seats, so it only fits a small team.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -990,8 +989,8 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>You'll probably always do some review, but it can be a two-minute skim instead of a reread. What cuts it down most is when every action item has a timestamp you can click to hear the original moment, so you only check the ones that look off. Saying owners and dates out loud at the end of the call helps a ton too.
-Disclosure, I work on Lynkk, which is built around that click-to-check idea. Honestly though, the verbal recap at the end helps with any tool.</t>
+          <t>Some review will always be needed, but it can be a two-minute skim. What cuts it down most is every action item having a timestamp you can click to hear the original moment, so you only check the ones that look off. Saying owners and dates out loud at the end of the call helps a lot too.
+Lynkk is built around that click-to-check idea: decisions, action items with owners and due dates, and open questions, each linked back to the recording.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1046,8 +1045,8 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Depends whether you need the meeting data inside your own agent or just need answers. If it's mostly 'what did we decide with X' and 'what's still open', asking inside the notes tool is simpler than wiring transcripts into an agent. If the agent needs to act on it alongside other context, then yeah, your MCP route makes sense.
-I work on Lynkk so I'm biased, but it's the first kind: you ask across your notes, get answers that link back to the moment, and can create a Jira issue from there. Not sure it fits if you need it inside your own agent.</t>
+          <t>Depends whether you need the meeting data inside your own agent or just need answers. If it's mostly 'what did we decide with X' and 'what's still open', asking inside the notes tool is simpler than wiring transcripts into an agent. If the agent has to act on it with other context, your MCP route makes sense.
+For the first case, Lynkk lets you ask across all your notes, gives answers that link back to the moment, and can create a Jira issue from there. You can ask it from Slack too.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1102,8 +1101,8 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Checking is the right call. What makes it workable is being able to click a line in the summary and hear the original moment, so checking a detail takes seconds instead of rereading the transcript. Small details are exactly where summaries slip, so I'd trust the summary for the gist and the recording for names and numbers.
-(I work on Lynkk, so bias disclosed. It does the click-to-hear thing, plus search across all your meetings afterwards.)</t>
+          <t>Checking is the right instinct. What makes it workable is clicking a line in the summary and hearing the original moment, so a detail takes seconds to verify instead of rereading the transcript. Trust the summary for the gist and the recording for names and numbers.
+Lynkk does the click-to-hear part: every takeaway and action item has a timestamp that plays the recording, and you can search across all your meetings afterwards.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1158,8 +1157,8 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>That 'inferred urgency' thing is exactly why action items need a source. Simplest rule: every action item links to the moment it was said, and anything without a source stays a draft. That catches invented deadlines in seconds. Also have owners confirm their own items instead of the PM approving everything.
-Disclosure, I work on Lynkk. Its action items each carry a timestamp back to the recording, and nothing goes to Jira unless someone sends it by hand.</t>
+          <t>That 'inferred urgency' is why action items need a source. Simplest rule: every action item links to the moment it was said, and anything without a source stays a draft. That catches invented deadlines in seconds. Also have owners confirm their own items instead of the PM approving everything.
+Lynkk works this way: each action item carries a timestamp back to the recording, and nothing goes to Jira unless someone sends it by hand.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1214,7 +1213,8 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Totally fair worry. Whatever you pick, export your recordings regularly so you're never stuck, and do a short side-by-side with a second tool before recommending anything firm-wide. (I work on Lynkk, so I'm one of the options. It's software only, so there's no hardware to bet on.)</t>
+          <t>Fair worry. Whatever you pick, export your recordings regularly so you're never stuck, and do a short side-by-side with a second tool before recommending anything firm-wide.
+If you want a software-only option to compare, Lynkk is one: no hardware to bet on, in-person recording from the browser, and calls through a Mac app.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1269,7 +1269,8 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Mostly depends on whether you have in-person meetings too. If you do, keep everything in one tool, otherwise you end up searching two places later. I'm on the Lynkk team, which does calls without a bot plus in-person from the browser, but I'd give the same advice for any tool.</t>
+          <t>Mostly depends on whether you have in-person meetings too. If you do, keep everything in one tool, otherwise you end up searching two places later.
+Lynkk is one that covers both: calls without a bot from a Mac app or Chrome extension, and in-person meetings from the browser.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1324,7 +1325,8 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Attendee-only is a good guardrail, but I'd go one step further: only set an owner when someone actually said it, with a link to that moment. Otherwise mark it 'owner needed'. A 30-second recap at the end ('Priya has the roadmap, Friday') removes most of the guessing. (Disclosure: I work on Lynkk, where every action item links back to the recording, which makes checking this pretty quick.)</t>
+          <t>Attendee-only is a good guardrail, but go one step further: only set an owner when someone actually said it, with a link to that moment, and otherwise mark it 'owner needed'. A 30-second recap at the end ('Priya has the roadmap, Friday') removes most of the guessing.
+Tools that link each action item to the recording make this quick to check; Lynkk does that for every action item.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1379,7 +1381,8 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Makes sense. If what you need is record, transcribe and summarize reliably, the agent features are just noise. I'd write down the three things you actually rely on and test alternatives against only those. (Biased, I work on Lynkk, which sticks to that core: recording, transcript, and a brief that links back to the audio.)</t>
+          <t>Makes sense. If what you need is record, transcribe and summarize reliably, the agent features are noise. Write down the three things you actually rely on and test alternatives against only those.
+Lynkk is worth adding to that test since it sticks to the core: recording, transcript, and a brief that links back to the audio.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1434,7 +1437,8 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Mixed language is rough for most engines. Setting the languages explicitly, if your tool lets you, and adding names and terms to a custom vocab usually helps more than anything. If you want a comparison point, I work on Lynkk, which does 17 languages with auto-detect plus a custom words list. Might be worth one side-by-side on a mixed meeting.</t>
+          <t>Mixed language is rough for most engines. Setting the languages explicitly, if your tool allows it, and adding names and terms to a custom vocabulary usually helps more than anything.
+For a comparison point, Lynkk transcribes 17 languages with auto-detect and has a custom words list. Worth one side-by-side on a mixed meeting.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1489,7 +1493,8 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>I'd start smaller than a coaching platform. Take five lost deals and five won ones and only listen from the first price mention onward. Patterns show up faster than you'd think. (I work on Lynkk. It's not a coaching tool, but its timestamps let you jump straight to the price discussion instead of replaying the whole hour, which might at least cut the review time.)</t>
+          <t>Start smaller than a coaching platform. Take five lost deals and five won ones and only listen from the first price mention onward; patterns show up faster than you'd expect.
+To cut the listening time, a tool with timestamped takeaways helps you jump straight to the price discussion. Lynkk does that, though it isn't a coaching tool, so it helps with the review time rather than scoring reps.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1544,7 +1549,8 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>The summary itself rarely saves time. What helps is when 'we could try this' gets filed as an open question instead of a decision, and you can click back to hear how it was actually said. (Disclosure: I work on Lynkk, which records without a bot too. Curious what other people find actually gets opened after the meeting.)</t>
+          <t>The summary itself rarely saves time. What helps is when 'we could try this' gets filed as an open question instead of a decision, and you can click back to hear how it was actually said.
+Lynkk splits decisions, action items and open questions that way and records without a bot, similar to what you like about Bluedot. Curious what others find actually gets opened after the meeting.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">

--- a/lynkk-reddit-leads/results/2026-10-11/reply_drafts_2026-10-11.xlsx
+++ b/lynkk-reddit-leads/results/2026-10-11/reply_drafts_2026-10-11.xlsx
@@ -427,20 +427,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1559,6 +1559,454 @@
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Self-promotion rule (banned, 10% rule, weekly thread only, or allowed with disclosure); whether links are allowed in comments; account age or karma minimums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/techadvice/comments/1w9auj0/looking_for_a_systemwide_dictation_app_for_mac_no/</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>r/techadvice</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>u/JanFromEarth</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Direct ask for Mac dictation; Lynkk's free Instant dictation fits the no-subscription wish.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Start with the built-in one: macOS Dictation works system-wide and costs nothing, so try it for a week and see where it annoys you (usually punctuation and names). If it's good enough, you're done.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Start with the built-in one: macOS Dictation works system-wide and costs nothing, so try it for a week and see where it annoys you (usually punctuation and names). If it's good enough, you're done.
+If you want something that cleans up better, Lynkk's Mac app has a free dictation mode: hold a key (fn by default), talk, and the text lands wherever your cursor is, in any app. The free Instant mode runs on the Mac and is English only; the cleaner modes that remove ums are on the paid plan, so try the free one first.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>If you want to try it, there's a free plan at lynkk.ai.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Self-promotion rule (banned, 10% rule, weekly thread only, or allowed with disclosure); whether links are allowed in comments; account age or karma minimums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/AiNoteTaker/comments/1wd79xs/which_ai_note_taker_are_you_using_for_meetings/</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>r/AiNoteTaker</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>u/Enough_Hippo1359</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Asks directly which AI note taker to use; good fit.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Speaker mix-ups are the main thing to test, so try each tool on a real meeting where people talk over each other, not a tidy demo. Also check whether you can jump from a line in the summary to that moment in the recording; it makes fixing a misheard word or a wrong name quick. If most of your meetings are online, a tool that records from your computer is easier than a separate recorder.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Speaker mix-ups are the main thing to test, so try each tool on a real meeting where people talk over each other, not a tidy demo. Also check whether you can jump from a line in the summary to that moment in the recording; it makes fixing a misheard word or a wrong name quick. If most of your meetings are online, a tool that records from your computer is easier than a separate recorder.
+Lynkk is one worth adding to the test: it records Zoom, Meet and Teams without a bot, keeps your own side on its own channel so it's labelled separately, and every takeaway in the summary links back to the recording.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>If you want to try it, there's a free plan at lynkk.ai.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Self-promotion rule (banned, 10% rule, weekly thread only, or allowed with disclosure); whether links are allowed in comments; account age or karma minimums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/ProductivityApps/comments/1vli8un/best_free_dictation_app_for_mac/</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>r/ProductivityApps</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>u/supersport604</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Direct ask for Mac dictation; Lynkk's free Instant mode fits. Don't promise unlimited.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Worth knowing what you liked about Wispr: if it's the cleanup (removing ums, fixing punctuation), the free options mostly don't do that well; if it's just speed and working in every app, plenty of free ones are fine.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Worth knowing what you liked about Wispr: if it's the cleanup (removing ums, fixing punctuation), the free options mostly don't do that well; if it's just speed and working in every app, plenty of free ones are fine.
+Lynkk's Mac app is one to try: hold a key (fn by default), talk, and the text appears wherever your cursor is. The basic Instant mode is free and runs on the Mac (English only), while the cleanup modes that remove ums are on the paid plan.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>If you want to try it, there's a free plan at lynkk.ai.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Self-promotion rule (banned, 10% rule, weekly thread only, or allowed with disclosure); whether links are allowed in comments; account age or karma minimums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/Zoom/comments/1wz5toq/best_ai_note_taker_for_zoom_across_two_client/</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>r/Zoom</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>u/CommissionBorn4257</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Clear buyer asking about admin control; note the 10 seat cap honestly.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>What usually breaks by month three is the stuff users can change without the admin: personal accounts recording customer calls, notes shared by public link, and local files left on laptops. Check three things on any tool: whether the company can see and retain notes made on company accounts, whether sharing links can be revoked, and whether audio lands in the cloud workspace rather than Downloads.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>What usually breaks by month three is the stuff users can change without the admin: personal accounts recording customer calls, notes shared by public link, and local files left on laptops. Check three things on any tool: whether the company can see and retain notes made on company accounts, whether sharing links can be revoked, and whether audio lands in the cloud workspace rather than Downloads.
+For small teams, Lynkk's workspaces handle that split well: admins can read workspace-visible notes, every admin read is logged, and people can mark a note personal. They cap at 10 seats though, so only if each client team is small.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>If you want to try it, there's a free plan at lynkk.ai.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Self-promotion rule (banned, 10% rule, weekly thread only, or allowed with disclosure); whether links are allowed in comments; account age or karma minimums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/ObsidianMD/comments/1vpg175/best_workflow_for_recording_inpersononline/</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>r/ObsidianMD</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>u/jnjsch</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Asks directly for a Granola alternative; be honest that the Obsidian sync part needs checking.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Since the sync part is what broke, I'd pick capture and Obsidian export separately. For capture, anything that records your mic and system audio without a bot covers online calls, and a laptop mic is fine for in-person. For the vault, the most durable setup is a tool that gives you plain text or Markdown you can paste or drop into a folder, so a plugin breaking can't strand your notes again.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Since the sync part is what broke, I'd pick capture and Obsidian export separately. For capture, anything that records your mic and system audio without a bot covers online calls, and a laptop mic is fine for in-person. For the vault, the most durable setup is a tool that gives you plain text or Markdown you can paste or drop into a folder, so a plugin breaking can't strand your notes again.
+Lynkk is one to look at for the capture side: no-bot recording for calls, in-person from the browser, and summaries with decisions and action items. Check how you'd get notes into the vault before committing, since there's no Obsidian plugin.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>If you want to try it, there's a free plan at lynkk.ai.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Self-promotion rule (banned, 10% rule, weekly thread only, or allowed with disclosure); whether links are allowed in comments; account age or karma minimums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/Entrepreneurs/comments/1wsbiws/otter_alternative_for_business_when_everyone_has/</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>r/Entrepreneurs</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>u/Big-Personality-9618</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Real business need; be honest that importing old Otter history isn't something Lynkk claims.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>On the migration worry: plan to export each person's Otter history to files before switching and store it centrally, rather than expecting a new tool to import it. Most don't do that cleanly, and it means the old history isn't hostage to whichever tool you choose. Then switch new meetings only, so people aren't asked to change everything at once.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>On the migration worry: plan to export each person's Otter history to files before switching and store it centrally, rather than expecting a new tool to import it. Most don't do that cleanly, and it means the old history isn't hostage to whichever tool you choose. Then switch new meetings only, so people aren't asked to change everything at once.
+For the management side on small teams, Lynkk's workspaces cover what you listed: colleagues join by company email domain, admins can read workspace-visible notes with every admin read logged, and people can still mark a note personal. They cap at 10 seats, so it fits small clients only.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>If you want to try it, there's a free plan at lynkk.ai.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Self-promotion rule (banned, 10% rule, weekly thread only, or allowed with disclosure); whether links are allowed in comments; account age or karma minimums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/ADHDers/comments/1w66wii/ai_note_taker_recommendations/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>r/ADHDers</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>u/Antics_Longhorn</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Asks directly for recommendations; keep it warm and practical.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>For a new job, the biggest win is being able to search everything later instead of relying on memory, so whatever you pick, make sure you can find 'what did they say about X' weeks later. Ask before recording people, and for training sessions it's usually welcome. Also, re-read the action items the same day; that's when it actually sticks.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>For a new job, the biggest win is being able to search everything later instead of relying on memory, so whatever you pick, make sure you can find 'what did they say about X' weeks later. Ask before recording people, and for training sessions it's usually welcome. Also, re-read the action items the same day; that's when it actually sticks.
+Lynkk is one to try: it records Zoom, Meet and Teams without a bot joining, gives you takeaways and action items after each meeting, and you can search across all of them. There's a free plan, so you can see if it suits you before paying.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>If you want to try it, there's a free plan at lynkk.ai.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Self-promotion rule (banned, 10% rule, weekly thread only, or allowed with disclosure); whether links are allowed in comments; account age or karma minimums.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.reddit.com/r/NoteTaking/comments/1wd8868/trying_to_pick_best_ai_meeting_note_taker/</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>r/NoteTaking</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>u/saxisa</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Not read: Reddit returned 403 for this subreddit's rules from this environment</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Clear buyer, but Lynkk only clearly meets the botless requirement; be honest about the rest.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Speaker naming is usually where the cheaper tools fall down, so I'd test that first with a real three-person call before anything else. Botless capture is common now, so it shouldn't be the deciding factor. And check whether the MCP access is on the plan you'd actually pay for, since a lot of tools keep it for higher tiers.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Speaker naming is usually where the cheaper tools fall down, so I'd test that first with a real three-person call before anything else. Botless capture is common now, so it shouldn't be the deciding factor. And check whether the MCP access is on the plan you'd actually pay for, since a lot of tools keep it for higher tiers.
+Lynkk is another one to put in the test: it records without a bot from a Mac app or a Chrome extension and labels your own side of the call separately. Worth checking its pricing and integrations against your list directly.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>If you want to try it, there's a free plan at lynkk.ai.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Self-promotion rule (banned, 10% rule, weekly thread only, or allowed with disclosure); whether links are allowed in comments; account age or karma minimums.</t>
         </is>
@@ -1585,6 +2033,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
